--- a/222/222_222/002_AES44/条件输入数据表.xlsx
+++ b/222/222_222/002_AES44/条件输入数据表.xlsx
@@ -1779,12 +1779,12 @@
       </c>
       <c r="D2" s="21" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>900</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>900</t>
         </is>
       </c>
       <c r="G2" s="10" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>英制系列</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>914</t>
         </is>
       </c>
     </row>
